--- a/analise_eua/tecnologia/microsoft/msft_indicators.xlsx
+++ b/analise_eua/tecnologia/microsoft/msft_indicators.xlsx
@@ -21,13 +21,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,13 +49,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,169 +436,169 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>P/L Damodaran</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>P/L</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>L/P</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Margem Líquida</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P/VPA</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Valor de Mercado</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Dívida Bruta</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Caixa e Equivalentes</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Dívida Líquida</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Dívida Líquida/EBITDA</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Dívida Líquida/PL</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FCO</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>FCI</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>FCF</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Capex</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Net Capex</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Adj Net Capex</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Working Capital</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Reinvestment Rate</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>FCFE</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>DPA</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Payout</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Buyback</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="B2" t="n">
-        <v>36.18</v>
+        <v>36.1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.18</v>
+        <v>36.1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="E2" t="n">
         <v>162681</v>
@@ -593,10 +607,10 @@
         <v>36.15</v>
       </c>
       <c r="G2" t="n">
-        <v>10.73</v>
+        <v>10.7</v>
       </c>
       <c r="H2" t="n">
-        <v>3684315110</v>
+        <v>3675915820</v>
       </c>
       <c r="I2" t="n">
         <v>112184</v>
@@ -614,7 +628,7 @@
         <v>0.05</v>
       </c>
       <c r="N2" t="n">
-        <v>22.76</v>
+        <v>22.7</v>
       </c>
       <c r="O2" t="n">
         <v>29.65</v>
@@ -669,17 +683,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
         <v>2024</v>
       </c>
       <c r="B3" t="n">
-        <v>37.27</v>
+        <v>37.18</v>
       </c>
       <c r="C3" t="n">
-        <v>37.27</v>
+        <v>37.18</v>
       </c>
       <c r="D3" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="E3" t="n">
         <v>131720</v>
@@ -688,10 +702,10 @@
         <v>35.96</v>
       </c>
       <c r="G3" t="n">
-        <v>12.23</v>
+        <v>12.21</v>
       </c>
       <c r="H3" t="n">
-        <v>3284427690</v>
+        <v>3276996690</v>
       </c>
       <c r="I3" t="n">
         <v>91159</v>
@@ -709,7 +723,7 @@
         <v>0.06</v>
       </c>
       <c r="N3" t="n">
-        <v>25.05</v>
+        <v>25</v>
       </c>
       <c r="O3" t="n">
         <v>32.83</v>
@@ -764,17 +778,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>2023</v>
       </c>
       <c r="B4" t="n">
-        <v>34.38</v>
+        <v>34.31</v>
       </c>
       <c r="C4" t="n">
-        <v>34.38</v>
+        <v>34.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="E4" t="n">
         <v>102384</v>
@@ -783,10 +797,10 @@
         <v>34.15</v>
       </c>
       <c r="G4" t="n">
-        <v>12.06</v>
+        <v>12.04</v>
       </c>
       <c r="H4" t="n">
-        <v>2488080900</v>
+        <v>2482421940</v>
       </c>
       <c r="I4" t="n">
         <v>79441</v>
@@ -804,7 +818,7 @@
         <v>-0.15</v>
       </c>
       <c r="N4" t="n">
-        <v>24.61</v>
+        <v>24.56</v>
       </c>
       <c r="O4" t="n">
         <v>35.09</v>
@@ -859,17 +873,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="B5" t="n">
-        <v>25.72</v>
+        <v>25.66</v>
       </c>
       <c r="C5" t="n">
-        <v>25.73</v>
+        <v>25.67</v>
       </c>
       <c r="D5" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="E5" t="n">
         <v>97843</v>
@@ -878,10 +892,10 @@
         <v>36.69</v>
       </c>
       <c r="G5" t="n">
-        <v>11.23</v>
+        <v>11.21</v>
       </c>
       <c r="H5" t="n">
-        <v>1871001600</v>
+        <v>1866728880</v>
       </c>
       <c r="I5" t="n">
         <v>78400</v>
@@ -899,7 +913,7 @@
         <v>-0.16</v>
       </c>
       <c r="N5" t="n">
-        <v>19.39</v>
+        <v>19.35</v>
       </c>
       <c r="O5" t="n">
         <v>43.68</v>
@@ -954,17 +968,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>2021</v>
       </c>
       <c r="B6" t="n">
-        <v>32.17</v>
+        <v>32.09</v>
       </c>
       <c r="C6" t="n">
-        <v>32.16</v>
+        <v>32.09</v>
       </c>
       <c r="D6" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="E6" t="n">
         <v>81602</v>
@@ -973,10 +987,10 @@
         <v>36.45</v>
       </c>
       <c r="G6" t="n">
-        <v>13.88</v>
+        <v>13.85</v>
       </c>
       <c r="H6" t="n">
-        <v>1970823580</v>
+        <v>1966295380</v>
       </c>
       <c r="I6" t="n">
         <v>82278</v>
@@ -994,7 +1008,7 @@
         <v>-0.34</v>
       </c>
       <c r="N6" t="n">
-        <v>24.74</v>
+        <v>24.69</v>
       </c>
       <c r="O6" t="n">
         <v>43.15</v>
@@ -1049,14 +1063,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>2020</v>
       </c>
       <c r="B7" t="n">
-        <v>33.39</v>
+        <v>33.31</v>
       </c>
       <c r="C7" t="n">
-        <v>33.38</v>
+        <v>33.31</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -1068,10 +1082,10 @@
         <v>30.96</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5</v>
+        <v>12.47</v>
       </c>
       <c r="H7" t="n">
-        <v>1478623000</v>
+        <v>1475198500</v>
       </c>
       <c r="I7" t="n">
         <v>82110</v>
@@ -1089,7 +1103,7 @@
         <v>-0.46</v>
       </c>
       <c r="N7" t="n">
-        <v>23.31</v>
+        <v>23.26</v>
       </c>
       <c r="O7" t="n">
         <v>37.43</v>
@@ -1144,17 +1158,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>2019</v>
       </c>
       <c r="B8" t="n">
-        <v>24.7</v>
+        <v>24.65</v>
       </c>
       <c r="C8" t="n">
-        <v>24.72</v>
+        <v>24.67</v>
       </c>
       <c r="D8" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="E8" t="n">
         <v>54641</v>
@@ -1163,10 +1177,10 @@
         <v>31.18</v>
       </c>
       <c r="G8" t="n">
-        <v>9.470000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>969406820.0000001</v>
+        <v>967181650</v>
       </c>
       <c r="I8" t="n">
         <v>86455</v>
@@ -1184,7 +1198,7 @@
         <v>-0.46</v>
       </c>
       <c r="N8" t="n">
-        <v>18.61</v>
+        <v>18.57</v>
       </c>
       <c r="O8" t="n">
         <v>38.35</v>
@@ -1239,14 +1253,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>2018</v>
       </c>
       <c r="B9" t="n">
-        <v>42.53</v>
+        <v>42.43</v>
       </c>
       <c r="C9" t="n">
-        <v>42.57</v>
+        <v>42.47</v>
       </c>
       <c r="D9" t="n">
         <v>2.35</v>
@@ -1258,10 +1272,10 @@
         <v>15.02</v>
       </c>
       <c r="G9" t="n">
-        <v>8.52</v>
+        <v>8.5</v>
       </c>
       <c r="H9" t="n">
-        <v>704704000</v>
+        <v>703087000</v>
       </c>
       <c r="I9" t="n">
         <v>87508</v>
@@ -1279,7 +1293,7 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>16.57</v>
+        <v>16.53</v>
       </c>
       <c r="O9" t="n">
         <v>20.03</v>
@@ -1334,17 +1348,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>2017</v>
       </c>
       <c r="B10" t="n">
-        <v>22.92</v>
+        <v>22.87</v>
       </c>
       <c r="C10" t="n">
-        <v>22.9</v>
+        <v>22.85</v>
       </c>
       <c r="D10" t="n">
-        <v>4.37</v>
+        <v>4.38</v>
       </c>
       <c r="E10" t="n">
         <v>31104</v>
@@ -1353,10 +1367,10 @@
         <v>37.08</v>
       </c>
       <c r="G10" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>486061500</v>
+        <v>484899600.0000001</v>
       </c>
       <c r="I10" t="n">
         <v>86455</v>
@@ -1374,7 +1388,7 @@
         <v>-0.64</v>
       </c>
       <c r="N10" t="n">
-        <v>17.12</v>
+        <v>17.09</v>
       </c>
       <c r="O10" t="n">
         <v>29.29</v>
@@ -1439,1773 +1453,1868 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>P/L Damodaran</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>P/L</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>L/P</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Margem Líquida</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P/VPA</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Valor de Mercado</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Dívida Bruta</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Caixa e Equivalentes</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Dívida Líquida</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Dívida Líquida/EBITDA</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Dívida Líquida/PL</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FCO</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>FCI</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>FCF</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Capex</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Net Capex</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Adj Net Capex</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Working Capital</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Reinvestment Rate</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>FCFE</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>DPA</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Payout</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Buyback</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46022</v>
+      <c r="A2" s="2" t="n">
+        <v>46112</v>
       </c>
       <c r="B2" t="n">
-        <v>93.45</v>
+        <v>86.5</v>
       </c>
       <c r="C2" t="n">
-        <v>30.96</v>
+        <v>22.22</v>
       </c>
       <c r="D2" t="n">
-        <v>3.23</v>
+        <v>4.5</v>
       </c>
       <c r="E2" t="n">
-        <v>34412</v>
+        <v>39367</v>
       </c>
       <c r="F2" t="n">
-        <v>47.32</v>
+        <v>38.34</v>
       </c>
       <c r="G2" t="n">
-        <v>9.19</v>
+        <v>6.63</v>
       </c>
       <c r="H2" t="n">
-        <v>3593780220</v>
+        <v>2748882420</v>
       </c>
       <c r="I2" t="n">
-        <v>123278</v>
+        <v>125432</v>
       </c>
       <c r="J2" t="n">
-        <v>89462</v>
+        <v>78272</v>
       </c>
       <c r="K2" t="n">
-        <v>33816</v>
+        <v>47160</v>
       </c>
       <c r="L2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="N2" t="n">
-        <v>24.11</v>
+        <v>17.62</v>
       </c>
       <c r="O2" t="n">
-        <v>29.71</v>
+        <v>29.88</v>
       </c>
       <c r="P2" t="n">
-        <v>21.93</v>
+        <v>21.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>-9299</v>
+        <v>10921</v>
       </c>
       <c r="R2" t="n">
-        <v>11854</v>
+        <v>-4700</v>
       </c>
       <c r="S2" t="n">
-        <v>-5818</v>
+        <v>6266</v>
       </c>
       <c r="T2" t="n">
-        <v>-19781</v>
+        <v>9921</v>
       </c>
       <c r="U2" t="n">
-        <v>10482</v>
+        <v>1000</v>
       </c>
       <c r="V2" t="n">
-        <v>21143</v>
+        <v>19737</v>
       </c>
       <c r="W2" t="n">
-        <v>8504</v>
+        <v>8915</v>
       </c>
       <c r="X2" t="n">
-        <v>53908</v>
+        <v>53500</v>
       </c>
       <c r="Y2" t="n">
-        <v>50185</v>
+        <v>38668</v>
       </c>
       <c r="Z2" t="n">
-        <v>54.43</v>
+        <v>40.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>88997</v>
+        <v>107337</v>
       </c>
       <c r="AB2" t="n">
-        <v>82907</v>
+        <v>104228</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.08</v>
+        <v>-0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.54</v>
+        <v>-0.02</v>
       </c>
       <c r="AE2" t="n">
-        <v>1765</v>
+        <v>-2788</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>45930</v>
+      <c r="A3" s="2" t="n">
+        <v>46022</v>
       </c>
       <c r="B3" t="n">
-        <v>138.49</v>
+        <v>93.23</v>
       </c>
       <c r="C3" t="n">
-        <v>37.57</v>
+        <v>30.89</v>
       </c>
       <c r="D3" t="n">
-        <v>2.66</v>
+        <v>3.24</v>
       </c>
       <c r="E3" t="n">
-        <v>51022</v>
+        <v>34412</v>
       </c>
       <c r="F3" t="n">
-        <v>35.72</v>
+        <v>47.32</v>
       </c>
       <c r="G3" t="n">
-        <v>10.58</v>
+        <v>9.17</v>
       </c>
       <c r="H3" t="n">
-        <v>3842712340</v>
+        <v>3585606120</v>
       </c>
       <c r="I3" t="n">
-        <v>120375</v>
+        <v>123278</v>
       </c>
       <c r="J3" t="n">
-        <v>102012</v>
+        <v>89462</v>
       </c>
       <c r="K3" t="n">
-        <v>18363</v>
+        <v>33816</v>
       </c>
       <c r="L3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="N3" t="n">
-        <v>25.08</v>
+        <v>24.06</v>
       </c>
       <c r="O3" t="n">
-        <v>28.19</v>
+        <v>29.71</v>
       </c>
       <c r="P3" t="n">
-        <v>22.59</v>
+        <v>21.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>45057</v>
+        <v>-9299</v>
       </c>
       <c r="R3" t="n">
-        <v>-34559</v>
+        <v>11854</v>
       </c>
       <c r="S3" t="n">
-        <v>-11799</v>
+        <v>-5818</v>
       </c>
       <c r="T3" t="n">
-        <v>25663</v>
+        <v>-19781</v>
       </c>
       <c r="U3" t="n">
-        <v>19394</v>
+        <v>10482</v>
       </c>
       <c r="V3" t="n">
-        <v>14338</v>
+        <v>21143</v>
       </c>
       <c r="W3" t="n">
-        <v>8146</v>
+        <v>8504</v>
       </c>
       <c r="X3" t="n">
-        <v>46143</v>
+        <v>53908</v>
       </c>
       <c r="Y3" t="n">
-        <v>54070</v>
+        <v>50185</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.17</v>
+        <v>54.43</v>
       </c>
       <c r="AA3" t="n">
-        <v>88031</v>
+        <v>88997</v>
       </c>
       <c r="AB3" t="n">
-        <v>94848</v>
+        <v>82907</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.83</v>
+        <v>0.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>22.23</v>
+        <v>1.54</v>
       </c>
       <c r="AE3" t="n">
-        <v>5650</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>45747</v>
+      <c r="A4" s="2" t="n">
+        <v>45930</v>
       </c>
       <c r="B4" t="n">
-        <v>107.49</v>
+        <v>138.18</v>
       </c>
       <c r="C4" t="n">
-        <v>28.77</v>
+        <v>37.49</v>
       </c>
       <c r="D4" t="n">
-        <v>3.48</v>
+        <v>2.67</v>
       </c>
       <c r="E4" t="n">
-        <v>33913</v>
+        <v>51022</v>
       </c>
       <c r="F4" t="n">
-        <v>36.86</v>
+        <v>35.72</v>
       </c>
       <c r="G4" t="n">
-        <v>8.619999999999999</v>
+        <v>10.56</v>
       </c>
       <c r="H4" t="n">
-        <v>2775781260</v>
+        <v>3834015730</v>
       </c>
       <c r="I4" t="n">
-        <v>105019</v>
+        <v>120375</v>
       </c>
       <c r="J4" t="n">
-        <v>79618</v>
+        <v>102012</v>
       </c>
       <c r="K4" t="n">
-        <v>25401</v>
+        <v>18363</v>
       </c>
       <c r="L4" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="N4" t="n">
-        <v>21.45</v>
+        <v>25.02</v>
       </c>
       <c r="O4" t="n">
-        <v>29.99</v>
+        <v>28.19</v>
       </c>
       <c r="P4" t="n">
-        <v>23.56</v>
+        <v>22.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>14753</v>
+        <v>45057</v>
       </c>
       <c r="R4" t="n">
-        <v>1398</v>
+        <v>-34559</v>
       </c>
       <c r="S4" t="n">
-        <v>-1793</v>
+        <v>-11799</v>
       </c>
       <c r="T4" t="n">
-        <v>13812</v>
+        <v>25663</v>
       </c>
       <c r="U4" t="n">
-        <v>941</v>
+        <v>19394</v>
       </c>
       <c r="V4" t="n">
-        <v>9154</v>
+        <v>14338</v>
       </c>
       <c r="W4" t="n">
-        <v>8198</v>
+        <v>8146</v>
       </c>
       <c r="X4" t="n">
-        <v>40466</v>
+        <v>46143</v>
       </c>
       <c r="Y4" t="n">
-        <v>42438</v>
+        <v>54070</v>
       </c>
       <c r="Z4" t="n">
-        <v>27.8</v>
+        <v>40.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>89227</v>
+        <v>88031</v>
       </c>
       <c r="AB4" t="n">
-        <v>103586</v>
+        <v>94848</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0</v>
+        <v>0.83</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>22.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>-205</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>45657</v>
+      <c r="A5" s="2" t="n">
+        <v>45747</v>
       </c>
       <c r="B5" t="n">
-        <v>129.04</v>
+        <v>107.24</v>
       </c>
       <c r="C5" t="n">
-        <v>33.61</v>
+        <v>28.7</v>
       </c>
       <c r="D5" t="n">
-        <v>2.98</v>
+        <v>3.48</v>
       </c>
       <c r="E5" t="n">
-        <v>31097</v>
+        <v>33913</v>
       </c>
       <c r="F5" t="n">
-        <v>34.62</v>
+        <v>36.86</v>
       </c>
       <c r="G5" t="n">
-        <v>10.28</v>
+        <v>8.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3110878350</v>
+        <v>2769462360</v>
       </c>
       <c r="I5" t="n">
-        <v>102909</v>
+        <v>105019</v>
       </c>
       <c r="J5" t="n">
-        <v>71555</v>
+        <v>79618</v>
       </c>
       <c r="K5" t="n">
-        <v>31354</v>
+        <v>25401</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="N5" t="n">
-        <v>24.99</v>
+        <v>21.4</v>
       </c>
       <c r="O5" t="n">
-        <v>30.59</v>
+        <v>29.99</v>
       </c>
       <c r="P5" t="n">
-        <v>23.8</v>
+        <v>23.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>-11889</v>
+        <v>14753</v>
       </c>
       <c r="R5" t="n">
-        <v>1089</v>
+        <v>1398</v>
       </c>
       <c r="S5" t="n">
-        <v>5333</v>
+        <v>-1793</v>
       </c>
       <c r="T5" t="n">
-        <v>-12770</v>
+        <v>13812</v>
       </c>
       <c r="U5" t="n">
-        <v>881</v>
+        <v>941</v>
       </c>
       <c r="V5" t="n">
-        <v>7906</v>
+        <v>9154</v>
       </c>
       <c r="W5" t="n">
-        <v>7917</v>
+        <v>8198</v>
       </c>
       <c r="X5" t="n">
-        <v>38162</v>
+        <v>40466</v>
       </c>
       <c r="Y5" t="n">
-        <v>38198</v>
+        <v>42438</v>
       </c>
       <c r="Z5" t="n">
-        <v>52.11</v>
+        <v>27.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>76618</v>
+        <v>89227</v>
       </c>
       <c r="AB5" t="n">
-        <v>75867</v>
+        <v>103586</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.08</v>
+        <v>-0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.47</v>
+        <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>879</v>
+        <v>-205</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>45565</v>
+      <c r="A6" s="2" t="n">
+        <v>45657</v>
       </c>
       <c r="B6" t="n">
-        <v>128.46</v>
+        <v>128.75</v>
       </c>
       <c r="C6" t="n">
-        <v>34.91</v>
+        <v>33.53</v>
       </c>
       <c r="D6" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="E6" t="n">
-        <v>37935</v>
+        <v>31097</v>
       </c>
       <c r="F6" t="n">
-        <v>37.61</v>
+        <v>34.62</v>
       </c>
       <c r="G6" t="n">
-        <v>11.01</v>
+        <v>10.25</v>
       </c>
       <c r="H6" t="n">
-        <v>3168687900</v>
+        <v>3103815100</v>
       </c>
       <c r="I6" t="n">
-        <v>96838</v>
+        <v>102909</v>
       </c>
       <c r="J6" t="n">
-        <v>78428</v>
+        <v>71555</v>
       </c>
       <c r="K6" t="n">
-        <v>18410</v>
+        <v>31354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="N6" t="n">
-        <v>25.4</v>
+        <v>24.93</v>
       </c>
       <c r="O6" t="n">
-        <v>31.55</v>
+        <v>30.59</v>
       </c>
       <c r="P6" t="n">
-        <v>23.93</v>
+        <v>23.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>34180</v>
+        <v>-11889</v>
       </c>
       <c r="R6" t="n">
-        <v>-15201</v>
+        <v>1089</v>
       </c>
       <c r="S6" t="n">
-        <v>-16576</v>
+        <v>5333</v>
       </c>
       <c r="T6" t="n">
-        <v>19257</v>
+        <v>-12770</v>
       </c>
       <c r="U6" t="n">
-        <v>14923</v>
+        <v>881</v>
       </c>
       <c r="V6" t="n">
-        <v>12465</v>
+        <v>7906</v>
       </c>
       <c r="W6" t="n">
-        <v>7544</v>
+        <v>7917</v>
       </c>
       <c r="X6" t="n">
-        <v>41463</v>
+        <v>38162</v>
       </c>
       <c r="Y6" t="n">
-        <v>34726</v>
+        <v>38198</v>
       </c>
       <c r="Z6" t="n">
-        <v>45.69</v>
+        <v>52.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>61966</v>
+        <v>76618</v>
       </c>
       <c r="AB6" t="n">
-        <v>78279</v>
+        <v>75867</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.75</v>
+        <v>0.08</v>
       </c>
       <c r="AD6" t="n">
-        <v>22.6</v>
+        <v>2.47</v>
       </c>
       <c r="AE6" t="n">
-        <v>4107</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>45382</v>
+      <c r="A7" s="2" t="n">
+        <v>45565</v>
       </c>
       <c r="B7" t="n">
-        <v>140.67</v>
+        <v>128.16</v>
       </c>
       <c r="C7" t="n">
-        <v>36.59</v>
+        <v>34.83</v>
       </c>
       <c r="D7" t="n">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="E7" t="n">
-        <v>27649</v>
+        <v>37935</v>
       </c>
       <c r="F7" t="n">
-        <v>35.47</v>
+        <v>37.61</v>
       </c>
       <c r="G7" t="n">
-        <v>12.19</v>
+        <v>10.99</v>
       </c>
       <c r="H7" t="n">
-        <v>3086168610</v>
+        <v>3161403560</v>
       </c>
       <c r="I7" t="n">
-        <v>85694</v>
+        <v>96838</v>
       </c>
       <c r="J7" t="n">
-        <v>80021</v>
+        <v>78428</v>
       </c>
       <c r="K7" t="n">
-        <v>5673</v>
+        <v>18410</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="N7" t="n">
-        <v>28.16</v>
+        <v>25.34</v>
       </c>
       <c r="O7" t="n">
-        <v>33.34</v>
+        <v>31.55</v>
       </c>
       <c r="P7" t="n">
-        <v>25.1</v>
+        <v>23.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>13064</v>
+        <v>34180</v>
       </c>
       <c r="R7" t="n">
-        <v>61225</v>
+        <v>-15201</v>
       </c>
       <c r="S7" t="n">
-        <v>-8661</v>
+        <v>-16576</v>
       </c>
       <c r="T7" t="n">
-        <v>11847</v>
+        <v>19257</v>
       </c>
       <c r="U7" t="n">
-        <v>1217</v>
+        <v>14923</v>
       </c>
       <c r="V7" t="n">
-        <v>5357</v>
+        <v>12465</v>
       </c>
       <c r="W7" t="n">
-        <v>7653</v>
+        <v>7544</v>
       </c>
       <c r="X7" t="n">
-        <v>33795</v>
+        <v>41463</v>
       </c>
       <c r="Y7" t="n">
-        <v>28655</v>
+        <v>34726</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.21</v>
+        <v>45.69</v>
       </c>
       <c r="AA7" t="n">
-        <v>83946</v>
+        <v>61966</v>
       </c>
       <c r="AB7" t="n">
-        <v>93098</v>
+        <v>78279</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0</v>
+        <v>0.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.01</v>
+        <v>22.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>213</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>45291</v>
+      <c r="A8" s="2" t="n">
+        <v>45382</v>
       </c>
       <c r="B8" t="n">
-        <v>125.91</v>
+        <v>140.35</v>
       </c>
       <c r="C8" t="n">
-        <v>34.95</v>
+        <v>36.51</v>
       </c>
       <c r="D8" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="E8" t="n">
-        <v>29070</v>
+        <v>27649</v>
       </c>
       <c r="F8" t="n">
-        <v>35.26</v>
+        <v>35.47</v>
       </c>
       <c r="G8" t="n">
-        <v>11.56</v>
+        <v>12.16</v>
       </c>
       <c r="H8" t="n">
-        <v>2753704640</v>
+        <v>3079109160</v>
       </c>
       <c r="I8" t="n">
-        <v>84317</v>
+        <v>85694</v>
       </c>
       <c r="J8" t="n">
-        <v>81017</v>
+        <v>80021</v>
       </c>
       <c r="K8" t="n">
-        <v>3300</v>
+        <v>5673</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="N8" t="n">
-        <v>26.66</v>
+        <v>28.1</v>
       </c>
       <c r="O8" t="n">
-        <v>33.11</v>
+        <v>33.34</v>
       </c>
       <c r="P8" t="n">
-        <v>24.41</v>
+        <v>25.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>-11730</v>
+        <v>13064</v>
       </c>
       <c r="R8" t="n">
-        <v>-72428</v>
+        <v>61225</v>
       </c>
       <c r="S8" t="n">
-        <v>-24908</v>
+        <v>-8661</v>
       </c>
       <c r="T8" t="n">
-        <v>-11548</v>
+        <v>11847</v>
       </c>
       <c r="U8" t="n">
-        <v>-182</v>
+        <v>1217</v>
       </c>
       <c r="V8" t="n">
-        <v>3341</v>
+        <v>5357</v>
       </c>
       <c r="W8" t="n">
-        <v>7142</v>
+        <v>7653</v>
       </c>
       <c r="X8" t="n">
-        <v>30970</v>
+        <v>33795</v>
       </c>
       <c r="Y8" t="n">
-        <v>26377</v>
+        <v>28655</v>
       </c>
       <c r="Z8" t="n">
-        <v>56.92</v>
+        <v>24.21</v>
       </c>
       <c r="AA8" t="n">
-        <v>62059</v>
+        <v>83946</v>
       </c>
       <c r="AB8" t="n">
-        <v>62516</v>
+        <v>93098</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.39</v>
+        <v>-0.01</v>
       </c>
       <c r="AE8" t="n">
-        <v>-831</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>45199</v>
+      <c r="A9" s="2" t="n">
+        <v>45291</v>
       </c>
       <c r="B9" t="n">
-        <v>103.47</v>
+        <v>125.62</v>
       </c>
       <c r="C9" t="n">
-        <v>31.02</v>
+        <v>34.87</v>
       </c>
       <c r="D9" t="n">
-        <v>3.22</v>
+        <v>2.87</v>
       </c>
       <c r="E9" t="n">
-        <v>30816</v>
+        <v>29070</v>
       </c>
       <c r="F9" t="n">
-        <v>39.44</v>
+        <v>35.26</v>
       </c>
       <c r="G9" t="n">
-        <v>10.45</v>
+        <v>11.53</v>
       </c>
       <c r="H9" t="n">
-        <v>2306555920</v>
+        <v>2747387440</v>
       </c>
       <c r="I9" t="n">
-        <v>79873</v>
+        <v>84317</v>
       </c>
       <c r="J9" t="n">
-        <v>143951</v>
+        <v>81017</v>
       </c>
       <c r="K9" t="n">
-        <v>-64078</v>
+        <v>3300</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.65</v>
+        <v>0.03</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.29</v>
+        <v>0.01</v>
       </c>
       <c r="N9" t="n">
-        <v>24.03</v>
+        <v>26.6</v>
       </c>
       <c r="O9" t="n">
-        <v>33.79</v>
+        <v>33.11</v>
       </c>
       <c r="P9" t="n">
-        <v>24.57</v>
+        <v>24.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>30583</v>
+        <v>-11730</v>
       </c>
       <c r="R9" t="n">
-        <v>503</v>
+        <v>-72428</v>
       </c>
       <c r="S9" t="n">
-        <v>14761</v>
+        <v>-24908</v>
       </c>
       <c r="T9" t="n">
-        <v>20666</v>
+        <v>-11548</v>
       </c>
       <c r="U9" t="n">
-        <v>9917</v>
+        <v>-182</v>
       </c>
       <c r="V9" t="n">
-        <v>9054</v>
+        <v>3341</v>
       </c>
       <c r="W9" t="n">
-        <v>6659</v>
+        <v>7142</v>
       </c>
       <c r="X9" t="n">
-        <v>36169</v>
+        <v>30970</v>
       </c>
       <c r="Y9" t="n">
-        <v>82794</v>
+        <v>26377</v>
       </c>
       <c r="Z9" t="n">
-        <v>46.46</v>
+        <v>56.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>54248</v>
+        <v>62059</v>
       </c>
       <c r="AB9" t="n">
-        <v>67277</v>
+        <v>62516</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.68</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>22.66</v>
+        <v>2.39</v>
       </c>
       <c r="AE9" t="n">
-        <v>4831</v>
+        <v>-831</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>45016</v>
+      <c r="A10" s="2" t="n">
+        <v>45199</v>
       </c>
       <c r="B10" t="n">
-        <v>114.78</v>
+        <v>103.24</v>
       </c>
       <c r="C10" t="n">
-        <v>30.55</v>
+        <v>30.95</v>
       </c>
       <c r="D10" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="E10" t="n">
-        <v>22253</v>
+        <v>30816</v>
       </c>
       <c r="F10" t="n">
-        <v>34.62</v>
+        <v>39.44</v>
       </c>
       <c r="G10" t="n">
-        <v>10.79</v>
+        <v>10.43</v>
       </c>
       <c r="H10" t="n">
-        <v>2100371070</v>
+        <v>2301281330</v>
       </c>
       <c r="I10" t="n">
-        <v>79312</v>
+        <v>79873</v>
       </c>
       <c r="J10" t="n">
-        <v>104427</v>
+        <v>143951</v>
       </c>
       <c r="K10" t="n">
-        <v>-25115</v>
+        <v>-64078</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.28</v>
+        <v>-0.65</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.13</v>
+        <v>-0.29</v>
       </c>
       <c r="N10" t="n">
-        <v>24.03</v>
+        <v>23.98</v>
       </c>
       <c r="O10" t="n">
-        <v>35.45</v>
+        <v>33.79</v>
       </c>
       <c r="P10" t="n">
-        <v>25.13</v>
+        <v>24.57</v>
       </c>
       <c r="Q10" t="n">
-        <v>13268</v>
+        <v>30583</v>
       </c>
       <c r="R10" t="n">
-        <v>3886</v>
+        <v>503</v>
       </c>
       <c r="S10" t="n">
-        <v>1059</v>
+        <v>14761</v>
       </c>
       <c r="T10" t="n">
-        <v>12935</v>
+        <v>20666</v>
       </c>
       <c r="U10" t="n">
-        <v>333</v>
+        <v>9917</v>
       </c>
       <c r="V10" t="n">
-        <v>2256</v>
+        <v>9054</v>
       </c>
       <c r="W10" t="n">
-        <v>6984</v>
+        <v>6659</v>
       </c>
       <c r="X10" t="n">
-        <v>29018</v>
+        <v>36169</v>
       </c>
       <c r="Y10" t="n">
-        <v>78198</v>
+        <v>82794</v>
       </c>
       <c r="Z10" t="n">
-        <v>24.97</v>
+        <v>46.46</v>
       </c>
       <c r="AA10" t="n">
-        <v>74375</v>
+        <v>54248</v>
       </c>
       <c r="AB10" t="n">
-        <v>77870</v>
+        <v>67277</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0</v>
+        <v>0.68</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.04</v>
+        <v>22.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>4831</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>44926</v>
+      <c r="A11" s="2" t="n">
+        <v>45016</v>
       </c>
       <c r="B11" t="n">
-        <v>106.25</v>
+        <v>114.52</v>
       </c>
       <c r="C11" t="n">
-        <v>25.24</v>
+        <v>30.48</v>
       </c>
       <c r="D11" t="n">
-        <v>3.96</v>
+        <v>3.28</v>
       </c>
       <c r="E11" t="n">
-        <v>21257</v>
+        <v>22253</v>
       </c>
       <c r="F11" t="n">
-        <v>31.14</v>
+        <v>34.62</v>
       </c>
       <c r="G11" t="n">
-        <v>9.529999999999999</v>
+        <v>10.77</v>
       </c>
       <c r="H11" t="n">
-        <v>1745173220</v>
+        <v>2095608830</v>
       </c>
       <c r="I11" t="n">
-        <v>77985</v>
+        <v>79312</v>
       </c>
       <c r="J11" t="n">
-        <v>99508</v>
+        <v>104427</v>
       </c>
       <c r="K11" t="n">
-        <v>-21523</v>
+        <v>-25115</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.24</v>
+        <v>-0.28</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="N11" t="n">
-        <v>19.91</v>
+        <v>23.97</v>
       </c>
       <c r="O11" t="n">
-        <v>37.94</v>
+        <v>35.45</v>
       </c>
       <c r="P11" t="n">
-        <v>26.57</v>
+        <v>25.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>-12025</v>
+        <v>13268</v>
       </c>
       <c r="R11" t="n">
-        <v>-4018</v>
+        <v>3886</v>
       </c>
       <c r="S11" t="n">
-        <v>-466</v>
+        <v>1059</v>
       </c>
       <c r="T11" t="n">
-        <v>-12016</v>
+        <v>12935</v>
       </c>
       <c r="U11" t="n">
-        <v>-9</v>
+        <v>333</v>
       </c>
       <c r="V11" t="n">
-        <v>1595</v>
+        <v>2256</v>
       </c>
       <c r="W11" t="n">
-        <v>6844</v>
+        <v>6984</v>
       </c>
       <c r="X11" t="n">
-        <v>27131</v>
+        <v>29018</v>
       </c>
       <c r="Y11" t="n">
-        <v>76105</v>
+        <v>78198</v>
       </c>
       <c r="Z11" t="n">
-        <v>56.88</v>
+        <v>24.97</v>
       </c>
       <c r="AA11" t="n">
-        <v>55424</v>
+        <v>74375</v>
       </c>
       <c r="AB11" t="n">
-        <v>54333</v>
+        <v>77870</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.06</v>
+        <v>-0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.71</v>
+        <v>-0.04</v>
       </c>
       <c r="AE11" t="n">
-        <v>-114</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>44834</v>
+      <c r="A12" s="2" t="n">
+        <v>44926</v>
       </c>
       <c r="B12" t="n">
-        <v>96.34</v>
+        <v>106.01</v>
       </c>
       <c r="C12" t="n">
-        <v>23.12</v>
+        <v>25.18</v>
       </c>
       <c r="D12" t="n">
-        <v>4.33</v>
+        <v>3.97</v>
       </c>
       <c r="E12" t="n">
-        <v>24308</v>
+        <v>21257</v>
       </c>
       <c r="F12" t="n">
-        <v>35.03</v>
+        <v>31.14</v>
       </c>
       <c r="G12" t="n">
-        <v>9.74</v>
+        <v>9.51</v>
       </c>
       <c r="H12" t="n">
-        <v>1691396740</v>
+        <v>1741224190</v>
       </c>
       <c r="I12" t="n">
-        <v>77136</v>
+        <v>77985</v>
       </c>
       <c r="J12" t="n">
-        <v>107262</v>
+        <v>99508</v>
       </c>
       <c r="K12" t="n">
-        <v>-30126</v>
+        <v>-21523</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.33</v>
+        <v>-0.24</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="N12" t="n">
-        <v>18.93</v>
+        <v>19.86</v>
       </c>
       <c r="O12" t="n">
-        <v>42.38</v>
+        <v>37.94</v>
       </c>
       <c r="P12" t="n">
-        <v>29.17</v>
+        <v>26.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>23198</v>
+        <v>-12025</v>
       </c>
       <c r="R12" t="n">
-        <v>-3132</v>
+        <v>-4018</v>
       </c>
       <c r="S12" t="n">
-        <v>-10883</v>
+        <v>-466</v>
       </c>
       <c r="T12" t="n">
-        <v>16915</v>
+        <v>-12016</v>
       </c>
       <c r="U12" t="n">
-        <v>6283</v>
+        <v>-9</v>
       </c>
       <c r="V12" t="n">
-        <v>5060</v>
+        <v>1595</v>
       </c>
       <c r="W12" t="n">
-        <v>6628</v>
+        <v>6844</v>
       </c>
       <c r="X12" t="n">
-        <v>29351</v>
+        <v>27131</v>
       </c>
       <c r="Y12" t="n">
-        <v>73423</v>
+        <v>76105</v>
       </c>
       <c r="Z12" t="n">
-        <v>39.21</v>
+        <v>56.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>63979</v>
+        <v>55424</v>
       </c>
       <c r="AB12" t="n">
-        <v>64283</v>
+        <v>54333</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.62</v>
+        <v>0.06</v>
       </c>
       <c r="AD12" t="n">
-        <v>26.32</v>
+        <v>2.71</v>
       </c>
       <c r="AE12" t="n">
-        <v>5573</v>
+        <v>-114</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>44651</v>
+      <c r="A13" s="2" t="n">
+        <v>44834</v>
       </c>
       <c r="B13" t="n">
-        <v>133.9</v>
+        <v>96.13</v>
       </c>
       <c r="C13" t="n">
-        <v>31.43</v>
+        <v>23.07</v>
       </c>
       <c r="D13" t="n">
-        <v>3.18</v>
+        <v>4.33</v>
       </c>
       <c r="E13" t="n">
-        <v>20641</v>
+        <v>24308</v>
       </c>
       <c r="F13" t="n">
-        <v>33.89</v>
+        <v>35.03</v>
       </c>
       <c r="G13" t="n">
-        <v>13.75</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2239882490</v>
+        <v>1687593670</v>
       </c>
       <c r="I13" t="n">
-        <v>77981</v>
+        <v>77136</v>
       </c>
       <c r="J13" t="n">
-        <v>104693</v>
+        <v>107262</v>
       </c>
       <c r="K13" t="n">
-        <v>-26712</v>
+        <v>-30126</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="N13" t="n">
-        <v>27.03</v>
+        <v>18.89</v>
       </c>
       <c r="O13" t="n">
-        <v>43.86</v>
+        <v>42.38</v>
       </c>
       <c r="P13" t="n">
-        <v>29.43</v>
+        <v>29.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>10906</v>
+        <v>23198</v>
       </c>
       <c r="R13" t="n">
-        <v>-15010</v>
+        <v>-3132</v>
       </c>
       <c r="S13" t="n">
-        <v>-5359</v>
+        <v>-10883</v>
       </c>
       <c r="T13" t="n">
-        <v>11431</v>
+        <v>16915</v>
       </c>
       <c r="U13" t="n">
-        <v>-525</v>
+        <v>6283</v>
       </c>
       <c r="V13" t="n">
-        <v>2307</v>
+        <v>5060</v>
       </c>
       <c r="W13" t="n">
-        <v>6306</v>
+        <v>6628</v>
       </c>
       <c r="X13" t="n">
-        <v>25174</v>
+        <v>29351</v>
       </c>
       <c r="Y13" t="n">
-        <v>76483</v>
+        <v>73423</v>
       </c>
       <c r="Z13" t="n">
-        <v>18.24</v>
+        <v>39.21</v>
       </c>
       <c r="AA13" t="n">
-        <v>79946</v>
+        <v>63979</v>
       </c>
       <c r="AB13" t="n">
-        <v>76135</v>
+        <v>64283</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0</v>
+        <v>0.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.04</v>
+        <v>26.32</v>
       </c>
       <c r="AE13" t="n">
-        <v>1389</v>
+        <v>5573</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>44561</v>
+      <c r="A14" s="2" t="n">
+        <v>44651</v>
       </c>
       <c r="B14" t="n">
-        <v>130.15</v>
+        <v>133.6</v>
       </c>
       <c r="C14" t="n">
-        <v>34.88</v>
+        <v>31.36</v>
       </c>
       <c r="D14" t="n">
-        <v>2.87</v>
+        <v>3.19</v>
       </c>
       <c r="E14" t="n">
-        <v>22531</v>
+        <v>20641</v>
       </c>
       <c r="F14" t="n">
-        <v>36.28</v>
+        <v>33.89</v>
       </c>
       <c r="G14" t="n">
-        <v>15.26</v>
+        <v>13.72</v>
       </c>
       <c r="H14" t="n">
-        <v>2442277100</v>
+        <v>2234787250</v>
       </c>
       <c r="I14" t="n">
-        <v>80353</v>
+        <v>77981</v>
       </c>
       <c r="J14" t="n">
-        <v>125369</v>
+        <v>104693</v>
       </c>
       <c r="K14" t="n">
-        <v>-45016</v>
+        <v>-26712</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.55</v>
+        <v>-0.32</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="N14" t="n">
-        <v>30.63</v>
+        <v>26.97</v>
       </c>
       <c r="O14" t="n">
-        <v>43.87</v>
+        <v>43.86</v>
       </c>
       <c r="P14" t="n">
-        <v>28.71</v>
+        <v>29.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10060</v>
+        <v>10906</v>
       </c>
       <c r="R14" t="n">
-        <v>2089</v>
+        <v>-15010</v>
       </c>
       <c r="S14" t="n">
-        <v>4290</v>
+        <v>-5359</v>
       </c>
       <c r="T14" t="n">
-        <v>-10115</v>
+        <v>11431</v>
       </c>
       <c r="U14" t="n">
-        <v>55</v>
+        <v>-525</v>
       </c>
       <c r="V14" t="n">
-        <v>2260</v>
+        <v>2307</v>
       </c>
       <c r="W14" t="n">
-        <v>5758</v>
+        <v>6306</v>
       </c>
       <c r="X14" t="n">
-        <v>23720</v>
+        <v>25174</v>
       </c>
       <c r="Y14" t="n">
-        <v>96678</v>
+        <v>76483</v>
       </c>
       <c r="Z14" t="n">
-        <v>47.21</v>
+        <v>18.24</v>
       </c>
       <c r="AA14" t="n">
-        <v>58574</v>
+        <v>79946</v>
       </c>
       <c r="AB14" t="n">
-        <v>53418</v>
+        <v>76135</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.06</v>
+        <v>-0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.38</v>
+        <v>-0.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>-251</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>44469</v>
+      <c r="A15" s="2" t="n">
+        <v>44561</v>
       </c>
       <c r="B15" t="n">
-        <v>99.76000000000001</v>
+        <v>129.85</v>
       </c>
       <c r="C15" t="n">
-        <v>31.4</v>
+        <v>34.8</v>
       </c>
       <c r="D15" t="n">
-        <v>3.18</v>
+        <v>2.87</v>
       </c>
       <c r="E15" t="n">
-        <v>23450</v>
+        <v>22531</v>
       </c>
       <c r="F15" t="n">
-        <v>45.25</v>
+        <v>36.28</v>
       </c>
       <c r="G15" t="n">
-        <v>13.46</v>
+        <v>15.23</v>
       </c>
       <c r="H15" t="n">
-        <v>2045639640</v>
+        <v>2436723400</v>
       </c>
       <c r="I15" t="n">
-        <v>78935</v>
+        <v>80353</v>
       </c>
       <c r="J15" t="n">
-        <v>130615</v>
+        <v>125369</v>
       </c>
       <c r="K15" t="n">
-        <v>-51680</v>
+        <v>-45016</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.67</v>
+        <v>-0.55</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.34</v>
+        <v>-0.28</v>
       </c>
       <c r="N15" t="n">
-        <v>27.16</v>
+        <v>30.56</v>
       </c>
       <c r="O15" t="n">
-        <v>42.98</v>
+        <v>43.87</v>
       </c>
       <c r="P15" t="n">
-        <v>27.78</v>
+        <v>28.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>24540</v>
+        <v>-10060</v>
       </c>
       <c r="R15" t="n">
-        <v>-3250</v>
+        <v>2089</v>
       </c>
       <c r="S15" t="n">
-        <v>-16276</v>
+        <v>4290</v>
       </c>
       <c r="T15" t="n">
-        <v>18730</v>
+        <v>-10115</v>
       </c>
       <c r="U15" t="n">
-        <v>5810</v>
+        <v>55</v>
       </c>
       <c r="V15" t="n">
-        <v>4751</v>
+        <v>2260</v>
       </c>
       <c r="W15" t="n">
-        <v>5599</v>
+        <v>5758</v>
       </c>
       <c r="X15" t="n">
-        <v>25379</v>
+        <v>23720</v>
       </c>
       <c r="Y15" t="n">
-        <v>93798</v>
+        <v>96678</v>
       </c>
       <c r="Z15" t="n">
-        <v>40.36</v>
+        <v>47.21</v>
       </c>
       <c r="AA15" t="n">
-        <v>54726</v>
+        <v>58574</v>
       </c>
       <c r="AB15" t="n">
-        <v>65727</v>
+        <v>53418</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AD15" t="n">
-        <v>20.51</v>
+        <v>2.38</v>
       </c>
       <c r="AE15" t="n">
-        <v>7684</v>
+        <v>-251</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>44286</v>
+      <c r="A16" s="2" t="n">
+        <v>44469</v>
       </c>
       <c r="B16" t="n">
-        <v>110.6</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>30.85</v>
+        <v>31.33</v>
       </c>
       <c r="D16" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="E16" t="n">
-        <v>17223</v>
+        <v>23450</v>
       </c>
       <c r="F16" t="n">
-        <v>37.06</v>
+        <v>45.25</v>
       </c>
       <c r="G16" t="n">
-        <v>12.71</v>
+        <v>13.43</v>
       </c>
       <c r="H16" t="n">
-        <v>1709468250</v>
+        <v>2040981580</v>
       </c>
       <c r="I16" t="n">
-        <v>81260</v>
+        <v>78935</v>
       </c>
       <c r="J16" t="n">
-        <v>125407</v>
+        <v>130615</v>
       </c>
       <c r="K16" t="n">
-        <v>-44147</v>
+        <v>-51680</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.66</v>
+        <v>-0.67</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
       <c r="N16" t="n">
-        <v>26.31</v>
+        <v>27.1</v>
       </c>
       <c r="O16" t="n">
-        <v>41.31</v>
+        <v>42.98</v>
       </c>
       <c r="P16" t="n">
-        <v>25.41</v>
+        <v>27.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>9663</v>
+        <v>24540</v>
       </c>
       <c r="R16" t="n">
-        <v>-8015</v>
+        <v>-3250</v>
       </c>
       <c r="S16" t="n">
-        <v>442</v>
+        <v>-16276</v>
       </c>
       <c r="T16" t="n">
-        <v>8748</v>
+        <v>18730</v>
       </c>
       <c r="U16" t="n">
-        <v>915</v>
+        <v>5810</v>
       </c>
       <c r="V16" t="n">
-        <v>2460</v>
+        <v>4751</v>
       </c>
       <c r="W16" t="n">
-        <v>5204</v>
+        <v>5599</v>
       </c>
       <c r="X16" t="n">
-        <v>22376</v>
+        <v>25379</v>
       </c>
       <c r="Y16" t="n">
-        <v>93421</v>
+        <v>93798</v>
       </c>
       <c r="Z16" t="n">
-        <v>23.43</v>
+        <v>40.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>59155</v>
+        <v>54726</v>
       </c>
       <c r="AB16" t="n">
-        <v>64283</v>
+        <v>65727</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.06</v>
+        <v>20.51</v>
       </c>
       <c r="AE16" t="n">
-        <v>395</v>
+        <v>7684</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>44196</v>
+      <c r="A17" s="2" t="n">
+        <v>44286</v>
       </c>
       <c r="B17" t="n">
-        <v>104.27</v>
+        <v>110.35</v>
       </c>
       <c r="C17" t="n">
-        <v>31.25</v>
+        <v>30.78</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="E17" t="n">
-        <v>18013</v>
+        <v>17223</v>
       </c>
       <c r="F17" t="n">
-        <v>35.9</v>
+        <v>37.06</v>
       </c>
       <c r="G17" t="n">
-        <v>12.38</v>
+        <v>12.68</v>
       </c>
       <c r="H17" t="n">
-        <v>1612388100</v>
+        <v>1705623360</v>
       </c>
       <c r="I17" t="n">
-        <v>82782</v>
+        <v>81260</v>
       </c>
       <c r="J17" t="n">
-        <v>131968</v>
+        <v>125407</v>
       </c>
       <c r="K17" t="n">
-        <v>-49186</v>
+        <v>-44147</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.77</v>
+        <v>-0.66</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.38</v>
+        <v>-0.33</v>
       </c>
       <c r="N17" t="n">
-        <v>26.15</v>
+        <v>26.25</v>
       </c>
       <c r="O17" t="n">
-        <v>39.74</v>
+        <v>41.31</v>
       </c>
       <c r="P17" t="n">
-        <v>23.94</v>
+        <v>25.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6819</v>
+        <v>9663</v>
       </c>
       <c r="R17" t="n">
-        <v>3702</v>
+        <v>-8015</v>
       </c>
       <c r="S17" t="n">
-        <v>-3345</v>
+        <v>442</v>
       </c>
       <c r="T17" t="n">
-        <v>-6086</v>
+        <v>8748</v>
       </c>
       <c r="U17" t="n">
-        <v>-733</v>
+        <v>915</v>
       </c>
       <c r="V17" t="n">
-        <v>1648</v>
+        <v>2460</v>
       </c>
       <c r="W17" t="n">
-        <v>4899</v>
+        <v>5204</v>
       </c>
       <c r="X17" t="n">
-        <v>20963</v>
+        <v>22376</v>
       </c>
       <c r="Y17" t="n">
-        <v>106487</v>
+        <v>93421</v>
       </c>
       <c r="Z17" t="n">
-        <v>57.55</v>
+        <v>23.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>37970</v>
+        <v>59155</v>
       </c>
       <c r="AB17" t="n">
-        <v>41098</v>
+        <v>64283</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.05</v>
+        <v>-0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.42</v>
+        <v>-0.06</v>
       </c>
       <c r="AE17" t="n">
-        <v>-208</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
+        <v>44196</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104.03</v>
+      </c>
+      <c r="C18" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E18" t="n">
+        <v>18013</v>
+      </c>
+      <c r="F18" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1608686150</v>
+      </c>
+      <c r="I18" t="n">
+        <v>82782</v>
+      </c>
+      <c r="J18" t="n">
+        <v>131968</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-49186</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="N18" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="O18" t="n">
+        <v>39.74</v>
+      </c>
+      <c r="P18" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-6819</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3702</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-3345</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-6086</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-733</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1648</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4899</v>
+      </c>
+      <c r="X18" t="n">
+        <v>20963</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>106487</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>37970</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>41098</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-208</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B18" t="n">
-        <v>109.62</v>
-      </c>
-      <c r="C18" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="B19" t="n">
+        <v>109.37</v>
+      </c>
+      <c r="C19" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E19" t="n">
         <v>18521</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>37.39</v>
       </c>
-      <c r="G18" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1522960140</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="G19" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1519479780</v>
+      </c>
+      <c r="I19" t="n">
         <v>83216</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>137977</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
         <v>-54761</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>-0.89</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M19" t="n">
         <v>-0.44</v>
       </c>
-      <c r="N18" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="N19" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="O19" t="n">
         <v>38.07</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P19" t="n">
         <v>22.58</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q19" t="n">
         <v>19335</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>-5371</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S19" t="n">
         <v>-10289</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>14428</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>4907</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V19" t="n">
         <v>2911</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W19" t="n">
         <v>4926</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X19" t="n">
         <v>21892</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y19" t="n">
         <v>107021</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z19" t="n">
         <v>43.77</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA19" t="n">
         <v>42530</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AB19" t="n">
         <v>46317</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AC19" t="n">
         <v>0.51</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD19" t="n">
         <v>27.75</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AE19" t="n">
         <v>6743</v>
       </c>
     </row>

--- a/analise_eua/tecnologia/microsoft/msft_indicators.xlsx
+++ b/analise_eua/tecnologia/microsoft/msft_indicators.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,856 +589,951 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B2" t="n">
-        <v>36.1</v>
+        <v>20.72</v>
       </c>
       <c r="C2" t="n">
-        <v>36.1</v>
+        <v>20.72</v>
       </c>
       <c r="D2" t="n">
-        <v>2.77</v>
+        <v>4.83</v>
       </c>
       <c r="E2" t="n">
-        <v>162681</v>
+        <v>193771</v>
       </c>
       <c r="F2" t="n">
-        <v>36.15</v>
+        <v>40.31</v>
       </c>
       <c r="G2" t="n">
-        <v>10.7</v>
+        <v>6.26</v>
       </c>
       <c r="H2" t="n">
-        <v>3675915820</v>
+        <v>2771165580</v>
       </c>
       <c r="I2" t="n">
-        <v>112184</v>
+        <v>128813</v>
       </c>
       <c r="J2" t="n">
-        <v>94565</v>
+        <v>76843</v>
       </c>
       <c r="K2" t="n">
-        <v>17619</v>
+        <v>51970</v>
       </c>
       <c r="L2" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="N2" t="n">
-        <v>22.7</v>
+        <v>14.57</v>
       </c>
       <c r="O2" t="n">
-        <v>29.65</v>
+        <v>30.23</v>
       </c>
       <c r="P2" t="n">
-        <v>23.42</v>
+        <v>21.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>136162</v>
+        <v>182935</v>
       </c>
       <c r="R2" t="n">
-        <v>-72599</v>
+        <v>-139500</v>
       </c>
       <c r="S2" t="n">
-        <v>-51699</v>
+        <v>-52546</v>
       </c>
       <c r="T2" t="n">
-        <v>71611</v>
+        <v>66987</v>
       </c>
       <c r="U2" t="n">
-        <v>64551</v>
+        <v>115948</v>
       </c>
       <c r="V2" t="n">
-        <v>30398</v>
+        <v>77414</v>
       </c>
       <c r="W2" t="n">
-        <v>32488</v>
+        <v>35562</v>
       </c>
       <c r="X2" t="n">
-        <v>62886</v>
+        <v>112976</v>
       </c>
       <c r="Y2" t="n">
-        <v>49913</v>
+        <v>38885</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.1</v>
+        <v>55.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>50066</v>
+        <v>62629</v>
       </c>
       <c r="AB2" t="n">
-        <v>63065</v>
+        <v>57007</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.24</v>
+        <v>3.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.65</v>
+        <v>19.77</v>
       </c>
       <c r="AE2" t="n">
-        <v>18420</v>
+        <v>22271</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B3" t="n">
-        <v>37.18</v>
+        <v>36.02</v>
       </c>
       <c r="C3" t="n">
-        <v>37.18</v>
+        <v>36.02</v>
       </c>
       <c r="D3" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="E3" t="n">
-        <v>131720</v>
+        <v>162681</v>
       </c>
       <c r="F3" t="n">
-        <v>35.96</v>
+        <v>36.15</v>
       </c>
       <c r="G3" t="n">
-        <v>12.21</v>
+        <v>10.68</v>
       </c>
       <c r="H3" t="n">
-        <v>3276996690</v>
+        <v>3667962510</v>
       </c>
       <c r="I3" t="n">
-        <v>91159</v>
+        <v>112184</v>
       </c>
       <c r="J3" t="n">
-        <v>75543</v>
+        <v>94565</v>
       </c>
       <c r="K3" t="n">
-        <v>15616</v>
+        <v>17619</v>
       </c>
       <c r="L3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>22.66</v>
       </c>
       <c r="O3" t="n">
-        <v>32.83</v>
+        <v>29.65</v>
       </c>
       <c r="P3" t="n">
-        <v>24.96</v>
+        <v>23.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>118548</v>
+        <v>136162</v>
       </c>
       <c r="R3" t="n">
-        <v>-96970</v>
+        <v>-72599</v>
       </c>
       <c r="S3" t="n">
-        <v>-37757</v>
+        <v>-51699</v>
       </c>
       <c r="T3" t="n">
-        <v>74071</v>
+        <v>71611</v>
       </c>
       <c r="U3" t="n">
-        <v>44477</v>
+        <v>64551</v>
       </c>
       <c r="V3" t="n">
-        <v>22190</v>
+        <v>30398</v>
       </c>
       <c r="W3" t="n">
-        <v>29510</v>
+        <v>32488</v>
       </c>
       <c r="X3" t="n">
-        <v>51700</v>
+        <v>62886</v>
       </c>
       <c r="Y3" t="n">
-        <v>34448</v>
+        <v>49913</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.96</v>
+        <v>40.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>53107</v>
+        <v>50066</v>
       </c>
       <c r="AB3" t="n">
-        <v>64378</v>
+        <v>63065</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.93</v>
+        <v>3.24</v>
       </c>
       <c r="AD3" t="n">
-        <v>24.7</v>
+        <v>23.65</v>
       </c>
       <c r="AE3" t="n">
-        <v>17254</v>
+        <v>18420</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B4" t="n">
-        <v>34.31</v>
+        <v>37.1</v>
       </c>
       <c r="C4" t="n">
-        <v>34.3</v>
+        <v>37.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="E4" t="n">
-        <v>102384</v>
+        <v>131720</v>
       </c>
       <c r="F4" t="n">
-        <v>34.15</v>
+        <v>35.96</v>
       </c>
       <c r="G4" t="n">
-        <v>12.04</v>
+        <v>12.18</v>
       </c>
       <c r="H4" t="n">
-        <v>2482421940</v>
+        <v>3269862930</v>
       </c>
       <c r="I4" t="n">
-        <v>79441</v>
+        <v>91159</v>
       </c>
       <c r="J4" t="n">
-        <v>111262</v>
+        <v>75543</v>
       </c>
       <c r="K4" t="n">
-        <v>-31821</v>
+        <v>15616</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.31</v>
+        <v>0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.15</v>
+        <v>0.06</v>
       </c>
       <c r="N4" t="n">
-        <v>24.56</v>
+        <v>24.94</v>
       </c>
       <c r="O4" t="n">
-        <v>35.09</v>
+        <v>32.83</v>
       </c>
       <c r="P4" t="n">
-        <v>25.05</v>
+        <v>24.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>87582</v>
+        <v>118548</v>
       </c>
       <c r="R4" t="n">
-        <v>-22680</v>
+        <v>-96970</v>
       </c>
       <c r="S4" t="n">
-        <v>-43935</v>
+        <v>-37757</v>
       </c>
       <c r="T4" t="n">
-        <v>59475</v>
+        <v>74071</v>
       </c>
       <c r="U4" t="n">
-        <v>28107</v>
+        <v>44477</v>
       </c>
       <c r="V4" t="n">
-        <v>14246</v>
+        <v>22190</v>
       </c>
       <c r="W4" t="n">
-        <v>27195</v>
+        <v>29510</v>
       </c>
       <c r="X4" t="n">
-        <v>41441</v>
+        <v>51700</v>
       </c>
       <c r="Y4" t="n">
-        <v>80108</v>
+        <v>34448</v>
       </c>
       <c r="Z4" t="n">
-        <v>31.71</v>
+        <v>27.96</v>
       </c>
       <c r="AA4" t="n">
-        <v>46918</v>
+        <v>53107</v>
       </c>
       <c r="AB4" t="n">
-        <v>49030</v>
+        <v>64378</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.66</v>
+        <v>2.93</v>
       </c>
       <c r="AD4" t="n">
-        <v>27.36</v>
+        <v>24.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>22245</v>
+        <v>17254</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B5" t="n">
-        <v>25.66</v>
+        <v>34.23</v>
       </c>
       <c r="C5" t="n">
-        <v>25.67</v>
+        <v>34.23</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="E5" t="n">
-        <v>97843</v>
+        <v>102384</v>
       </c>
       <c r="F5" t="n">
-        <v>36.69</v>
+        <v>34.15</v>
       </c>
       <c r="G5" t="n">
-        <v>11.21</v>
+        <v>12.01</v>
       </c>
       <c r="H5" t="n">
-        <v>1866728880</v>
+        <v>2477060820</v>
       </c>
       <c r="I5" t="n">
-        <v>78400</v>
+        <v>79441</v>
       </c>
       <c r="J5" t="n">
-        <v>104757</v>
+        <v>111262</v>
       </c>
       <c r="K5" t="n">
-        <v>-26357</v>
+        <v>-31821</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.27</v>
+        <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="N5" t="n">
-        <v>19.35</v>
+        <v>24.5</v>
       </c>
       <c r="O5" t="n">
-        <v>43.68</v>
+        <v>35.09</v>
       </c>
       <c r="P5" t="n">
-        <v>29.56</v>
+        <v>25.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>89035</v>
+        <v>87582</v>
       </c>
       <c r="R5" t="n">
-        <v>-30311</v>
+        <v>-22680</v>
       </c>
       <c r="S5" t="n">
-        <v>-58876</v>
+        <v>-43935</v>
       </c>
       <c r="T5" t="n">
-        <v>65149</v>
+        <v>59475</v>
       </c>
       <c r="U5" t="n">
-        <v>23886</v>
+        <v>28107</v>
       </c>
       <c r="V5" t="n">
-        <v>9426</v>
+        <v>14246</v>
       </c>
       <c r="W5" t="n">
-        <v>24512</v>
+        <v>27195</v>
       </c>
       <c r="X5" t="n">
-        <v>33938</v>
+        <v>41441</v>
       </c>
       <c r="Y5" t="n">
-        <v>74602</v>
+        <v>80108</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.28</v>
+        <v>31.71</v>
       </c>
       <c r="AA5" t="n">
-        <v>49033</v>
+        <v>46918</v>
       </c>
       <c r="AB5" t="n">
-        <v>57767</v>
+        <v>49030</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="AD5" t="n">
-        <v>24.93</v>
+        <v>27.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>32696</v>
+        <v>22245</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B6" t="n">
-        <v>32.09</v>
+        <v>25.61</v>
       </c>
       <c r="C6" t="n">
-        <v>32.09</v>
+        <v>25.62</v>
       </c>
       <c r="D6" t="n">
-        <v>3.12</v>
+        <v>3.9</v>
       </c>
       <c r="E6" t="n">
-        <v>81602</v>
+        <v>97843</v>
       </c>
       <c r="F6" t="n">
-        <v>36.45</v>
+        <v>36.69</v>
       </c>
       <c r="G6" t="n">
-        <v>13.85</v>
+        <v>11.18</v>
       </c>
       <c r="H6" t="n">
-        <v>1966295380</v>
+        <v>1862681040</v>
       </c>
       <c r="I6" t="n">
-        <v>82278</v>
+        <v>78400</v>
       </c>
       <c r="J6" t="n">
-        <v>130334</v>
+        <v>104757</v>
       </c>
       <c r="K6" t="n">
-        <v>-48056</v>
+        <v>-26357</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.59</v>
+        <v>-0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.34</v>
+        <v>-0.16</v>
       </c>
       <c r="N6" t="n">
-        <v>24.69</v>
+        <v>19.31</v>
       </c>
       <c r="O6" t="n">
-        <v>43.15</v>
+        <v>43.68</v>
       </c>
       <c r="P6" t="n">
-        <v>26.79</v>
+        <v>29.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>76740</v>
+        <v>89035</v>
       </c>
       <c r="R6" t="n">
-        <v>-27577</v>
+        <v>-30311</v>
       </c>
       <c r="S6" t="n">
-        <v>-48486</v>
+        <v>-58876</v>
       </c>
       <c r="T6" t="n">
-        <v>56118</v>
+        <v>65149</v>
       </c>
       <c r="U6" t="n">
-        <v>20622</v>
+        <v>23886</v>
       </c>
       <c r="V6" t="n">
-        <v>8936</v>
+        <v>9426</v>
       </c>
       <c r="W6" t="n">
-        <v>20716</v>
+        <v>24512</v>
       </c>
       <c r="X6" t="n">
-        <v>29652</v>
+        <v>33938</v>
       </c>
       <c r="Y6" t="n">
-        <v>95749</v>
+        <v>74602</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.68</v>
+        <v>20.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>47499</v>
+        <v>49033</v>
       </c>
       <c r="AB6" t="n">
-        <v>50227</v>
+        <v>57767</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.19</v>
+        <v>2.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>26.96</v>
+        <v>24.93</v>
       </c>
       <c r="AE6" t="n">
-        <v>27385</v>
+        <v>32696</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B7" t="n">
-        <v>33.31</v>
+        <v>32.02</v>
       </c>
       <c r="C7" t="n">
-        <v>33.31</v>
+        <v>32.02</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="E7" t="n">
-        <v>65755</v>
+        <v>81602</v>
       </c>
       <c r="F7" t="n">
-        <v>30.96</v>
+        <v>36.45</v>
       </c>
       <c r="G7" t="n">
-        <v>12.47</v>
+        <v>13.82</v>
       </c>
       <c r="H7" t="n">
-        <v>1475198500</v>
+        <v>1962069060</v>
       </c>
       <c r="I7" t="n">
-        <v>82110</v>
+        <v>82278</v>
       </c>
       <c r="J7" t="n">
-        <v>136527</v>
+        <v>130334</v>
       </c>
       <c r="K7" t="n">
-        <v>-54417</v>
+        <v>-48056</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.83</v>
+        <v>-0.59</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.46</v>
+        <v>-0.34</v>
       </c>
       <c r="N7" t="n">
-        <v>23.26</v>
+        <v>24.63</v>
       </c>
       <c r="O7" t="n">
-        <v>37.43</v>
+        <v>43.15</v>
       </c>
       <c r="P7" t="n">
-        <v>22.06</v>
+        <v>26.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>60675</v>
+        <v>76740</v>
       </c>
       <c r="R7" t="n">
-        <v>-12223</v>
+        <v>-27577</v>
       </c>
       <c r="S7" t="n">
-        <v>-46031</v>
+        <v>-48486</v>
       </c>
       <c r="T7" t="n">
-        <v>45234</v>
+        <v>56118</v>
       </c>
       <c r="U7" t="n">
-        <v>15441</v>
+        <v>20622</v>
       </c>
       <c r="V7" t="n">
-        <v>2645</v>
+        <v>8936</v>
       </c>
       <c r="W7" t="n">
-        <v>19269</v>
+        <v>20716</v>
       </c>
       <c r="X7" t="n">
-        <v>21914</v>
+        <v>29652</v>
       </c>
       <c r="Y7" t="n">
-        <v>109605</v>
+        <v>95749</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.31</v>
+        <v>16.68</v>
       </c>
       <c r="AA7" t="n">
-        <v>34646</v>
+        <v>47499</v>
       </c>
       <c r="AB7" t="n">
-        <v>40100</v>
+        <v>50227</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>34.18</v>
+        <v>26.96</v>
       </c>
       <c r="AE7" t="n">
-        <v>22968</v>
+        <v>27385</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B8" t="n">
-        <v>24.65</v>
+        <v>33.24</v>
       </c>
       <c r="C8" t="n">
-        <v>24.67</v>
+        <v>33.24</v>
       </c>
       <c r="D8" t="n">
-        <v>4.05</v>
+        <v>3.01</v>
       </c>
       <c r="E8" t="n">
-        <v>54641</v>
+        <v>65755</v>
       </c>
       <c r="F8" t="n">
-        <v>31.18</v>
+        <v>30.96</v>
       </c>
       <c r="G8" t="n">
-        <v>9.449999999999999</v>
+        <v>12.44</v>
       </c>
       <c r="H8" t="n">
-        <v>967181650</v>
+        <v>1472002300</v>
       </c>
       <c r="I8" t="n">
-        <v>86455</v>
+        <v>82110</v>
       </c>
       <c r="J8" t="n">
-        <v>133819</v>
+        <v>136527</v>
       </c>
       <c r="K8" t="n">
-        <v>-47364</v>
+        <v>-54417</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.87</v>
+        <v>-0.83</v>
       </c>
       <c r="M8" t="n">
         <v>-0.46</v>
       </c>
       <c r="N8" t="n">
-        <v>18.57</v>
+        <v>23.21</v>
       </c>
       <c r="O8" t="n">
-        <v>38.35</v>
+        <v>37.43</v>
       </c>
       <c r="P8" t="n">
-        <v>20.4</v>
+        <v>22.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>52185</v>
+        <v>60675</v>
       </c>
       <c r="R8" t="n">
-        <v>-15773</v>
+        <v>-12223</v>
       </c>
       <c r="S8" t="n">
-        <v>-36887</v>
+        <v>-46031</v>
       </c>
       <c r="T8" t="n">
-        <v>38260</v>
+        <v>45234</v>
       </c>
       <c r="U8" t="n">
-        <v>13925</v>
+        <v>15441</v>
       </c>
       <c r="V8" t="n">
-        <v>2243</v>
+        <v>2645</v>
       </c>
       <c r="W8" t="n">
-        <v>16876</v>
+        <v>19269</v>
       </c>
       <c r="X8" t="n">
-        <v>19119</v>
+        <v>21914</v>
       </c>
       <c r="Y8" t="n">
-        <v>106132</v>
+        <v>109605</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.57</v>
+        <v>9.31</v>
       </c>
       <c r="AA8" t="n">
-        <v>30400</v>
+        <v>34646</v>
       </c>
       <c r="AB8" t="n">
-        <v>33745</v>
+        <v>40100</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AD8" t="n">
-        <v>35.2</v>
+        <v>34.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>19543</v>
+        <v>22968</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B9" t="n">
-        <v>42.43</v>
+        <v>24.6</v>
       </c>
       <c r="C9" t="n">
-        <v>42.47</v>
+        <v>24.61</v>
       </c>
       <c r="D9" t="n">
-        <v>2.35</v>
+        <v>4.06</v>
       </c>
       <c r="E9" t="n">
-        <v>45319</v>
+        <v>54641</v>
       </c>
       <c r="F9" t="n">
-        <v>15.02</v>
+        <v>31.18</v>
       </c>
       <c r="G9" t="n">
-        <v>8.5</v>
+        <v>9.43</v>
       </c>
       <c r="H9" t="n">
-        <v>703087000</v>
+        <v>965109940.0000001</v>
       </c>
       <c r="I9" t="n">
-        <v>87508</v>
+        <v>86455</v>
       </c>
       <c r="J9" t="n">
-        <v>133768</v>
+        <v>133819</v>
       </c>
       <c r="K9" t="n">
-        <v>-46260</v>
+        <v>-47364</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.02</v>
+        <v>-0.87</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.46</v>
       </c>
       <c r="N9" t="n">
-        <v>16.53</v>
+        <v>18.53</v>
       </c>
       <c r="O9" t="n">
-        <v>20.03</v>
+        <v>38.35</v>
       </c>
       <c r="P9" t="n">
-        <v>8.9</v>
+        <v>20.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>43884</v>
+        <v>52185</v>
       </c>
       <c r="R9" t="n">
-        <v>-6061</v>
+        <v>-15773</v>
       </c>
       <c r="S9" t="n">
-        <v>-33590</v>
+        <v>-36887</v>
       </c>
       <c r="T9" t="n">
-        <v>32252</v>
+        <v>38260</v>
       </c>
       <c r="U9" t="n">
-        <v>11632</v>
+        <v>13925</v>
       </c>
       <c r="V9" t="n">
-        <v>1371</v>
+        <v>2243</v>
       </c>
       <c r="W9" t="n">
-        <v>14726</v>
+        <v>16876</v>
       </c>
       <c r="X9" t="n">
-        <v>16097</v>
+        <v>19119</v>
       </c>
       <c r="Y9" t="n">
-        <v>111174</v>
+        <v>106132</v>
       </c>
       <c r="Z9" t="n">
-        <v>-92.06999999999999</v>
+        <v>12.57</v>
       </c>
       <c r="AA9" t="n">
-        <v>20323</v>
+        <v>30400</v>
       </c>
       <c r="AB9" t="n">
-        <v>29881</v>
+        <v>33745</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>76.63</v>
+        <v>35.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>10721</v>
+        <v>19543</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B10" t="n">
+        <v>42.34</v>
+      </c>
+      <c r="C10" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E10" t="n">
+        <v>45319</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="H10" t="n">
+        <v>701547000</v>
+      </c>
+      <c r="I10" t="n">
+        <v>87508</v>
+      </c>
+      <c r="J10" t="n">
+        <v>133768</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-46260</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="N10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>43884</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-6061</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-33590</v>
+      </c>
+      <c r="T10" t="n">
+        <v>32252</v>
+      </c>
+      <c r="U10" t="n">
+        <v>11632</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1371</v>
+      </c>
+      <c r="W10" t="n">
+        <v>14726</v>
+      </c>
+      <c r="X10" t="n">
+        <v>16097</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>111174</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-92.06999999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>20323</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>29881</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>76.63</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>10721</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
         <v>2017</v>
       </c>
-      <c r="B10" t="n">
-        <v>22.87</v>
-      </c>
-      <c r="C10" t="n">
-        <v>22.85</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="B11" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="C11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="E11" t="n">
         <v>31104</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>37.08</v>
       </c>
-      <c r="G10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="H10" t="n">
-        <v>484899600.0000001</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="G11" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="H11" t="n">
+        <v>483892620</v>
+      </c>
+      <c r="I11" t="n">
         <v>86455</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>132981</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>-46526</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>-1.5</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" t="n">
         <v>-0.64</v>
       </c>
-      <c r="N10" t="n">
-        <v>17.09</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="N11" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="O11" t="n">
         <v>29.29</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P11" t="n">
         <v>12.83</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q11" t="n">
         <v>39507</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>-46781</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>8408</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>31378</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>8129</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V11" t="n">
         <v>-649</v>
       </c>
-      <c r="W10" t="n">
+      <c r="W11" t="n">
         <v>13037</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X11" t="n">
         <v>12388</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y11" t="n">
         <v>95324</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z11" t="n">
         <v>-22.65</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA11" t="n">
         <v>57280</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AB11" t="n">
         <v>25067</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC11" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD11" t="n">
         <v>55.86</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE11" t="n">
         <v>11788</v>
       </c>
     </row>
@@ -1613,13 +1708,13 @@
         <v>46112</v>
       </c>
       <c r="B2" t="n">
-        <v>86.5</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>22.22</v>
+        <v>22.17</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5</v>
+        <v>4.51</v>
       </c>
       <c r="E2" t="n">
         <v>39367</v>
@@ -1628,10 +1723,10 @@
         <v>38.34</v>
       </c>
       <c r="G2" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="H2" t="n">
-        <v>2748882420</v>
+        <v>2742941620</v>
       </c>
       <c r="I2" t="n">
         <v>125432</v>
@@ -1649,7 +1744,7 @@
         <v>0.11</v>
       </c>
       <c r="N2" t="n">
-        <v>17.62</v>
+        <v>17.58</v>
       </c>
       <c r="O2" t="n">
         <v>29.88</v>
@@ -1708,10 +1803,10 @@
         <v>46022</v>
       </c>
       <c r="B3" t="n">
-        <v>93.23</v>
+        <v>93.03</v>
       </c>
       <c r="C3" t="n">
-        <v>30.89</v>
+        <v>30.82</v>
       </c>
       <c r="D3" t="n">
         <v>3.24</v>
@@ -1723,10 +1818,10 @@
         <v>47.32</v>
       </c>
       <c r="G3" t="n">
-        <v>9.17</v>
+        <v>9.15</v>
       </c>
       <c r="H3" t="n">
-        <v>3585606120</v>
+        <v>3577877880</v>
       </c>
       <c r="I3" t="n">
         <v>123278</v>
@@ -1744,7 +1839,7 @@
         <v>0.09</v>
       </c>
       <c r="N3" t="n">
-        <v>24.06</v>
+        <v>24.01</v>
       </c>
       <c r="O3" t="n">
         <v>29.71</v>
@@ -1803,10 +1898,10 @@
         <v>45930</v>
       </c>
       <c r="B4" t="n">
-        <v>138.18</v>
+        <v>137.88</v>
       </c>
       <c r="C4" t="n">
-        <v>37.49</v>
+        <v>37.4</v>
       </c>
       <c r="D4" t="n">
         <v>2.67</v>
@@ -1818,10 +1913,10 @@
         <v>35.72</v>
       </c>
       <c r="G4" t="n">
-        <v>10.56</v>
+        <v>10.54</v>
       </c>
       <c r="H4" t="n">
-        <v>3834015730</v>
+        <v>3825690770</v>
       </c>
       <c r="I4" t="n">
         <v>120375</v>
@@ -1839,7 +1934,7 @@
         <v>0.05</v>
       </c>
       <c r="N4" t="n">
-        <v>25.02</v>
+        <v>24.97</v>
       </c>
       <c r="O4" t="n">
         <v>28.19</v>
@@ -1898,13 +1993,13 @@
         <v>45747</v>
       </c>
       <c r="B5" t="n">
-        <v>107.24</v>
+        <v>107.01</v>
       </c>
       <c r="C5" t="n">
-        <v>28.7</v>
+        <v>28.64</v>
       </c>
       <c r="D5" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="E5" t="n">
         <v>33913</v>
@@ -1913,10 +2008,10 @@
         <v>36.86</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>8.58</v>
       </c>
       <c r="H5" t="n">
-        <v>2769462360</v>
+        <v>2763440820</v>
       </c>
       <c r="I5" t="n">
         <v>105019</v>
@@ -1934,7 +2029,7 @@
         <v>0.08</v>
       </c>
       <c r="N5" t="n">
-        <v>21.4</v>
+        <v>21.36</v>
       </c>
       <c r="O5" t="n">
         <v>29.99</v>
@@ -1993,13 +2088,13 @@
         <v>45657</v>
       </c>
       <c r="B6" t="n">
-        <v>128.75</v>
+        <v>128.47</v>
       </c>
       <c r="C6" t="n">
-        <v>33.53</v>
+        <v>33.46</v>
       </c>
       <c r="D6" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="E6" t="n">
         <v>31097</v>
@@ -2008,10 +2103,10 @@
         <v>34.62</v>
       </c>
       <c r="G6" t="n">
-        <v>10.25</v>
+        <v>10.23</v>
       </c>
       <c r="H6" t="n">
-        <v>3103815100</v>
+        <v>3097123600</v>
       </c>
       <c r="I6" t="n">
         <v>102909</v>
@@ -2029,7 +2124,7 @@
         <v>0.1</v>
       </c>
       <c r="N6" t="n">
-        <v>24.93</v>
+        <v>24.88</v>
       </c>
       <c r="O6" t="n">
         <v>30.59</v>
@@ -2088,13 +2183,13 @@
         <v>45565</v>
       </c>
       <c r="B7" t="n">
-        <v>128.16</v>
+        <v>127.89</v>
       </c>
       <c r="C7" t="n">
-        <v>34.83</v>
+        <v>34.76</v>
       </c>
       <c r="D7" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="E7" t="n">
         <v>37935</v>
@@ -2103,10 +2198,10 @@
         <v>37.61</v>
       </c>
       <c r="G7" t="n">
-        <v>10.99</v>
+        <v>10.96</v>
       </c>
       <c r="H7" t="n">
-        <v>3161403560</v>
+        <v>3154639530</v>
       </c>
       <c r="I7" t="n">
         <v>96838</v>
@@ -2124,7 +2219,7 @@
         <v>0.06</v>
       </c>
       <c r="N7" t="n">
-        <v>25.34</v>
+        <v>25.29</v>
       </c>
       <c r="O7" t="n">
         <v>31.55</v>
@@ -2183,13 +2278,13 @@
         <v>45382</v>
       </c>
       <c r="B8" t="n">
-        <v>140.35</v>
+        <v>140.04</v>
       </c>
       <c r="C8" t="n">
-        <v>36.51</v>
+        <v>36.43</v>
       </c>
       <c r="D8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="E8" t="n">
         <v>27649</v>
@@ -2198,10 +2293,10 @@
         <v>35.47</v>
       </c>
       <c r="G8" t="n">
-        <v>12.16</v>
+        <v>12.14</v>
       </c>
       <c r="H8" t="n">
-        <v>3079109160</v>
+        <v>3072421260</v>
       </c>
       <c r="I8" t="n">
         <v>85694</v>
@@ -2219,7 +2314,7 @@
         <v>0.02</v>
       </c>
       <c r="N8" t="n">
-        <v>28.1</v>
+        <v>28.04</v>
       </c>
       <c r="O8" t="n">
         <v>33.34</v>
@@ -2278,10 +2373,10 @@
         <v>45291</v>
       </c>
       <c r="B9" t="n">
-        <v>125.62</v>
+        <v>125.35</v>
       </c>
       <c r="C9" t="n">
-        <v>34.87</v>
+        <v>34.8</v>
       </c>
       <c r="D9" t="n">
         <v>2.87</v>
@@ -2293,10 +2388,10 @@
         <v>35.26</v>
       </c>
       <c r="G9" t="n">
-        <v>11.53</v>
+        <v>11.51</v>
       </c>
       <c r="H9" t="n">
-        <v>2747387440</v>
+        <v>2741441840</v>
       </c>
       <c r="I9" t="n">
         <v>84317</v>
@@ -2314,7 +2409,7 @@
         <v>0.01</v>
       </c>
       <c r="N9" t="n">
-        <v>26.6</v>
+        <v>26.55</v>
       </c>
       <c r="O9" t="n">
         <v>33.11</v>
@@ -2373,13 +2468,13 @@
         <v>45199</v>
       </c>
       <c r="B10" t="n">
-        <v>103.24</v>
+        <v>103.01</v>
       </c>
       <c r="C10" t="n">
-        <v>30.95</v>
+        <v>30.88</v>
       </c>
       <c r="D10" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="E10" t="n">
         <v>30816</v>
@@ -2388,10 +2483,10 @@
         <v>39.44</v>
       </c>
       <c r="G10" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2301281330</v>
+        <v>2296303900</v>
       </c>
       <c r="I10" t="n">
         <v>79873</v>
@@ -2409,7 +2504,7 @@
         <v>-0.29</v>
       </c>
       <c r="N10" t="n">
-        <v>23.98</v>
+        <v>23.93</v>
       </c>
       <c r="O10" t="n">
         <v>33.79</v>
@@ -2468,13 +2563,13 @@
         <v>45016</v>
       </c>
       <c r="B11" t="n">
-        <v>114.52</v>
+        <v>114.27</v>
       </c>
       <c r="C11" t="n">
-        <v>30.48</v>
+        <v>30.41</v>
       </c>
       <c r="D11" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="E11" t="n">
         <v>22253</v>
@@ -2483,10 +2578,10 @@
         <v>34.62</v>
       </c>
       <c r="G11" t="n">
-        <v>10.77</v>
+        <v>10.74</v>
       </c>
       <c r="H11" t="n">
-        <v>2095608830</v>
+        <v>2091069820</v>
       </c>
       <c r="I11" t="n">
         <v>79312</v>
@@ -2504,7 +2599,7 @@
         <v>-0.13</v>
       </c>
       <c r="N11" t="n">
-        <v>23.97</v>
+        <v>23.92</v>
       </c>
       <c r="O11" t="n">
         <v>35.45</v>
@@ -2563,13 +2658,13 @@
         <v>44926</v>
       </c>
       <c r="B12" t="n">
-        <v>106.01</v>
+        <v>105.78</v>
       </c>
       <c r="C12" t="n">
-        <v>25.18</v>
+        <v>25.13</v>
       </c>
       <c r="D12" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="E12" t="n">
         <v>21257</v>
@@ -2578,10 +2673,10 @@
         <v>31.14</v>
       </c>
       <c r="G12" t="n">
-        <v>9.51</v>
+        <v>9.49</v>
       </c>
       <c r="H12" t="n">
-        <v>1741224190</v>
+        <v>1737424180</v>
       </c>
       <c r="I12" t="n">
         <v>77985</v>
@@ -2599,7 +2694,7 @@
         <v>-0.12</v>
       </c>
       <c r="N12" t="n">
-        <v>19.86</v>
+        <v>19.82</v>
       </c>
       <c r="O12" t="n">
         <v>37.94</v>
@@ -2658,13 +2753,13 @@
         <v>44834</v>
       </c>
       <c r="B13" t="n">
-        <v>96.13</v>
+        <v>95.92</v>
       </c>
       <c r="C13" t="n">
-        <v>23.07</v>
+        <v>23.02</v>
       </c>
       <c r="D13" t="n">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="E13" t="n">
         <v>24308</v>
@@ -2673,10 +2768,10 @@
         <v>35.03</v>
       </c>
       <c r="G13" t="n">
-        <v>9.720000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>1687593670</v>
+        <v>1683939740</v>
       </c>
       <c r="I13" t="n">
         <v>77136</v>
@@ -2694,7 +2789,7 @@
         <v>-0.17</v>
       </c>
       <c r="N13" t="n">
-        <v>18.89</v>
+        <v>18.85</v>
       </c>
       <c r="O13" t="n">
         <v>42.38</v>
@@ -2753,13 +2848,13 @@
         <v>44651</v>
       </c>
       <c r="B14" t="n">
-        <v>133.6</v>
+        <v>133.31</v>
       </c>
       <c r="C14" t="n">
-        <v>31.36</v>
+        <v>31.29</v>
       </c>
       <c r="D14" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="E14" t="n">
         <v>20641</v>
@@ -2768,10 +2863,10 @@
         <v>33.89</v>
       </c>
       <c r="G14" t="n">
-        <v>13.72</v>
+        <v>13.69</v>
       </c>
       <c r="H14" t="n">
-        <v>2234787250</v>
+        <v>2229991730</v>
       </c>
       <c r="I14" t="n">
         <v>77981</v>
@@ -2789,7 +2884,7 @@
         <v>-0.16</v>
       </c>
       <c r="N14" t="n">
-        <v>26.97</v>
+        <v>26.92</v>
       </c>
       <c r="O14" t="n">
         <v>43.86</v>
@@ -2848,13 +2943,13 @@
         <v>44561</v>
       </c>
       <c r="B15" t="n">
-        <v>129.85</v>
+        <v>129.57</v>
       </c>
       <c r="C15" t="n">
-        <v>34.8</v>
+        <v>34.72</v>
       </c>
       <c r="D15" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="E15" t="n">
         <v>22531</v>
@@ -2863,10 +2958,10 @@
         <v>36.28</v>
       </c>
       <c r="G15" t="n">
-        <v>15.23</v>
+        <v>15.2</v>
       </c>
       <c r="H15" t="n">
-        <v>2436723400</v>
+        <v>2431394850</v>
       </c>
       <c r="I15" t="n">
         <v>80353</v>
@@ -2884,7 +2979,7 @@
         <v>-0.28</v>
       </c>
       <c r="N15" t="n">
-        <v>30.56</v>
+        <v>30.49</v>
       </c>
       <c r="O15" t="n">
         <v>43.87</v>
@@ -2943,13 +3038,13 @@
         <v>44469</v>
       </c>
       <c r="B16" t="n">
-        <v>99.54000000000001</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>31.33</v>
+        <v>31.27</v>
       </c>
       <c r="D16" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="E16" t="n">
         <v>23450</v>
@@ -2958,10 +3053,10 @@
         <v>45.25</v>
       </c>
       <c r="G16" t="n">
-        <v>13.43</v>
+        <v>13.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2040981580</v>
+        <v>2036624040</v>
       </c>
       <c r="I16" t="n">
         <v>78935</v>
@@ -2979,7 +3074,7 @@
         <v>-0.34</v>
       </c>
       <c r="N16" t="n">
-        <v>27.1</v>
+        <v>27.05</v>
       </c>
       <c r="O16" t="n">
         <v>42.98</v>
@@ -3038,13 +3133,13 @@
         <v>44286</v>
       </c>
       <c r="B17" t="n">
-        <v>110.35</v>
+        <v>110.11</v>
       </c>
       <c r="C17" t="n">
-        <v>30.78</v>
+        <v>30.71</v>
       </c>
       <c r="D17" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="E17" t="n">
         <v>17223</v>
@@ -3053,10 +3148,10 @@
         <v>37.06</v>
       </c>
       <c r="G17" t="n">
-        <v>12.68</v>
+        <v>12.65</v>
       </c>
       <c r="H17" t="n">
-        <v>1705623360</v>
+        <v>1701929250</v>
       </c>
       <c r="I17" t="n">
         <v>81260</v>
@@ -3074,7 +3169,7 @@
         <v>-0.33</v>
       </c>
       <c r="N17" t="n">
-        <v>26.25</v>
+        <v>26.2</v>
       </c>
       <c r="O17" t="n">
         <v>41.31</v>
@@ -3133,10 +3228,10 @@
         <v>44196</v>
       </c>
       <c r="B18" t="n">
-        <v>104.03</v>
+        <v>103.81</v>
       </c>
       <c r="C18" t="n">
-        <v>31.18</v>
+        <v>31.11</v>
       </c>
       <c r="D18" t="n">
         <v>3.21</v>
@@ -3148,10 +3243,10 @@
         <v>35.9</v>
       </c>
       <c r="G18" t="n">
-        <v>12.35</v>
+        <v>12.32</v>
       </c>
       <c r="H18" t="n">
-        <v>1608686150</v>
+        <v>1605210850</v>
       </c>
       <c r="I18" t="n">
         <v>82782</v>
@@ -3169,7 +3264,7 @@
         <v>-0.38</v>
       </c>
       <c r="N18" t="n">
-        <v>26.09</v>
+        <v>26.03</v>
       </c>
       <c r="O18" t="n">
         <v>39.74</v>
@@ -3228,10 +3323,10 @@
         <v>44104</v>
       </c>
       <c r="B19" t="n">
-        <v>109.37</v>
+        <v>109.14</v>
       </c>
       <c r="C19" t="n">
-        <v>32.5</v>
+        <v>32.43</v>
       </c>
       <c r="D19" t="n">
         <v>3.08</v>
@@ -3243,10 +3338,10 @@
         <v>37.39</v>
       </c>
       <c r="G19" t="n">
-        <v>12.31</v>
+        <v>12.29</v>
       </c>
       <c r="H19" t="n">
-        <v>1519479780</v>
+        <v>1516226400</v>
       </c>
       <c r="I19" t="n">
         <v>83216</v>
@@ -3264,7 +3359,7 @@
         <v>-0.44</v>
       </c>
       <c r="N19" t="n">
-        <v>25.73</v>
+        <v>25.67</v>
       </c>
       <c r="O19" t="n">
         <v>38.07</v>
